--- a/GRAMMAR/6_19_12.xlsx
+++ b/GRAMMAR/6_19_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022A1278-DD8C-4777-B59F-50C941E31457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2EAA64-8E12-4562-9561-92F57F74C1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8505" yWindow="1605" windowWidth="23580" windowHeight="17835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Fre</t>
   </si>
@@ -39,12 +39,78 @@
     <t>备注</t>
   </si>
   <si>
+    <t>N+の末に</t>
+  </si>
+  <si>
+    <t>经过...之后，最终...</t>
+  </si>
+  <si>
+    <t>N+のすえに</t>
+  </si>
+  <si>
+    <t>ようがない</t>
+  </si>
+  <si>
+    <t>没法...，无法...</t>
+  </si>
+  <si>
+    <t>〜である</t>
+  </si>
+  <si>
+    <t>是...（です的书面语）</t>
+  </si>
+  <si>
+    <t>ところだった</t>
+  </si>
+  <si>
+    <t>差一点就...</t>
+  </si>
+  <si>
+    <t>落ち込んだ</t>
+  </si>
+  <si>
+    <t>心情低落，消沉</t>
+  </si>
+  <si>
+    <t>おちこんだ</t>
+  </si>
+  <si>
+    <t>“落ち着かせる”使…平静</t>
+  </si>
+  <si>
+    <t>もとで</t>
+  </si>
+  <si>
+    <t>在...之下</t>
+  </si>
+  <si>
     <t>どういたしまして</t>
   </si>
   <si>
     <t>不客气</t>
   </si>
   <si>
+    <t>看病</t>
+  </si>
+  <si>
+    <t>护理，照顾</t>
+  </si>
+  <si>
+    <t>かんびょう</t>
+  </si>
+  <si>
+    <t>よほど</t>
+  </si>
+  <si>
+    <t>很，颇，相当</t>
+  </si>
+  <si>
+    <t>おすすめです</t>
+  </si>
+  <si>
+    <t>推荐</t>
+  </si>
+  <si>
     <t>中身</t>
   </si>
   <si>
@@ -54,52 +120,97 @@
     <t>なかみ</t>
   </si>
   <si>
+    <t>〜に決まる</t>
+  </si>
+  <si>
+    <t>一定是...，肯定是...</t>
+  </si>
+  <si>
+    <t>〜にきまる</t>
+  </si>
+  <si>
+    <t>同“～に違いない”</t>
+  </si>
+  <si>
+    <t>直る</t>
+  </si>
+  <si>
+    <t>修好；改正</t>
+  </si>
+  <si>
+    <t>なおる</t>
+  </si>
+  <si>
+    <t>このたび</t>
+  </si>
+  <si>
+    <t>此次，这次</t>
+  </si>
+  <si>
+    <t>〜に応じて</t>
+  </si>
+  <si>
+    <t>根据...，按照...</t>
+  </si>
+  <si>
+    <t>〜におうじて</t>
+  </si>
+  <si>
+    <t>“～にこたえて”响应</t>
+  </si>
+  <si>
+    <t>持ち歩く</t>
+  </si>
+  <si>
+    <t>随身携带</t>
+  </si>
+  <si>
+    <t>もちあるく</t>
+  </si>
+  <si>
+    <t>“持参”携带</t>
+  </si>
+  <si>
+    <t>急な雨</t>
+  </si>
+  <si>
+    <t>急雨，阵雨</t>
+  </si>
+  <si>
+    <t>きゅうなあめ</t>
+  </si>
+  <si>
+    <t>おそらく〜でしょう・だろう</t>
+  </si>
+  <si>
+    <t>大概...吧，恐怕...吧</t>
+  </si>
+  <si>
+    <t>どうか</t>
+  </si>
+  <si>
+    <t>请，设法</t>
+  </si>
+  <si>
     <t>ものにする</t>
   </si>
   <si>
     <t>选择</t>
   </si>
   <si>
-    <t>请，设法</t>
-  </si>
-  <si>
-    <t>よほど</t>
-  </si>
-  <si>
-    <t>很，颇，相当</t>
-  </si>
-  <si>
-    <t>落ち込んだ</t>
-  </si>
-  <si>
-    <t>心情低落，消沉</t>
-  </si>
-  <si>
-    <t>おちこんだ</t>
-  </si>
-  <si>
-    <t>“落ち着かせる”使…平静</t>
+    <t>みたいだ</t>
   </si>
   <si>
     <t>好像...，像...一样</t>
   </si>
   <si>
-    <t>ところだった</t>
-  </si>
-  <si>
-    <t>差一点就...</t>
-  </si>
-  <si>
-    <t>ようがない</t>
-  </si>
-  <si>
-    <t>没法...，无法...</t>
-  </si>
-  <si>
-    <t>もとで</t>
-  </si>
-  <si>
-    <t>在...之下</t>
+    <t>話</t>
+  </si>
+  <si>
+    <t>这件事</t>
+  </si>
+  <si>
+    <t>はなし</t>
   </si>
   <si>
     <t>って</t>
@@ -108,111 +219,6 @@
     <t>（口语）表示引用或主题</t>
   </si>
   <si>
-    <t>N+の末に</t>
-  </si>
-  <si>
-    <t>经过...之后，最终...</t>
-  </si>
-  <si>
-    <t>N+のすえに</t>
-  </si>
-  <si>
-    <t>〜に決まる</t>
-  </si>
-  <si>
-    <t>一定是...，肯定是...</t>
-  </si>
-  <si>
-    <t>〜にきまる</t>
-  </si>
-  <si>
-    <t>同“～に違いない”</t>
-  </si>
-  <si>
-    <t>このたび</t>
-  </si>
-  <si>
-    <t>此次，这次</t>
-  </si>
-  <si>
-    <t>〜である</t>
-  </si>
-  <si>
-    <t>是...（です的书面语）</t>
-  </si>
-  <si>
-    <t>看病</t>
-  </si>
-  <si>
-    <t>护理，照顾</t>
-  </si>
-  <si>
-    <t>かんびょう</t>
-  </si>
-  <si>
-    <t>おすすめです</t>
-  </si>
-  <si>
-    <t>推荐</t>
-  </si>
-  <si>
-    <t>持ち歩く</t>
-  </si>
-  <si>
-    <t>随身携带</t>
-  </si>
-  <si>
-    <t>もちあるく</t>
-  </si>
-  <si>
-    <t>“持参”携带</t>
-  </si>
-  <si>
-    <t>話</t>
-  </si>
-  <si>
-    <t>这件事</t>
-  </si>
-  <si>
-    <t>はなし</t>
-  </si>
-  <si>
-    <t>〜に応じて</t>
-  </si>
-  <si>
-    <t>根据...，按照...</t>
-  </si>
-  <si>
-    <t>〜におうじて</t>
-  </si>
-  <si>
-    <t>“～にこたえて”响应</t>
-  </si>
-  <si>
-    <t>直る</t>
-  </si>
-  <si>
-    <t>修好；改正</t>
-  </si>
-  <si>
-    <t>なおる</t>
-  </si>
-  <si>
-    <t>急な雨</t>
-  </si>
-  <si>
-    <t>急雨，阵雨</t>
-  </si>
-  <si>
-    <t>きゅうなあめ</t>
-  </si>
-  <si>
-    <t>おそらく〜でしょう・だろう</t>
-  </si>
-  <si>
-    <t>大概...吧，恐怕...吧</t>
-  </si>
-  <si>
     <t>もと</t>
   </si>
   <si>
@@ -229,22 +235,6 @@
   </si>
   <si>
     <t>“わけではない”并不是</t>
-  </si>
-  <si>
-    <t>“どう”怎样；如何</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>どうか</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>みたいだ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>“〜てみたい”想试着做某事看看</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -622,7 +612,7 @@
     <col min="2" max="2" width="25.625" customWidth="1"/>
     <col min="3" max="3" width="19.125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="22.625" customWidth="1"/>
+    <col min="5" max="5" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
@@ -644,7 +634,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -652,24 +642,24 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -680,69 +670,66 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
@@ -750,21 +737,21 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
@@ -772,41 +759,44 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
@@ -814,10 +804,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
@@ -825,10 +815,16 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
@@ -836,13 +832,16 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
@@ -850,10 +849,13 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
@@ -861,47 +863,32 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
@@ -909,13 +896,10 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
@@ -923,13 +907,13 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
@@ -937,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
@@ -948,27 +932,27 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/GRAMMAR/6_19_12.xlsx
+++ b/GRAMMAR/6_19_12.xlsx
@@ -466,33 +466,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>よほど</t>
+          <t>N+の末に</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>很，颇，相当</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>经过...之后，最终...</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N+のすえに</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>もとで</t>
+          <t>ところだった</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>在...之下</t>
+          <t>差一点就...</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -500,16 +504,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>どうか</t>
+          <t>もとで</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>请，设法</t>
+          <t>在...之下</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -521,12 +525,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ものにする</t>
+          <t>どういたしまして</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>选择</t>
+          <t>不客气</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -538,28 +542,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>〜に決まる</t>
+          <t>よほど</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>一定是...，肯定是...</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>〜にきまる</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>同“～に違いない”</t>
-        </is>
-      </c>
+          <t>很，颇，相当</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -580,37 +576,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N+の末に</t>
+          <t>ものにする</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>经过...之后，最终...</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N+のすえに</t>
-        </is>
-      </c>
+          <t>选择</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>どういたしまして</t>
+          <t>どうか</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>不客气</t>
+          <t>请，设法</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -618,43 +610,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ところだった</t>
+          <t>持ち歩く</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>差一点就...</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>随身携带</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>もちあるく</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>“持参”携带</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>落ち込んだ</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>心情低落，消沉</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>おちこんだ</t>
-        </is>
-      </c>
+          <t>根源,原因</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>“落ち着かせる”使…平静</t>
+          <t>“もっと”更加…;更进一步</t>
         </is>
       </c>
     </row>
@@ -664,19 +660,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>看病</t>
+          <t>って</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>护理，照顾</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>かんびょう</t>
-        </is>
-      </c>
+          <t>（口语）表示引用或主题</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -685,37 +677,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>〜に応じて</t>
+          <t>話</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>根据...，按照...</t>
+          <t>这件事</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>〜におうじて</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>“～にこたえて”响应</t>
-        </is>
-      </c>
+          <t>はなし</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>〜である</t>
+          <t>みたいだ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>是...（です的书面语）</t>
+          <t>好像...，像...一样</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -727,12 +715,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>おすすめです</t>
+          <t>おそらく〜でしょう・だろう</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>推荐</t>
+          <t>大概...吧，恐怕...吧</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -744,15 +732,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ようがない</t>
+          <t>急な雨</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>没法...，无法...</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>急雨，阵雨</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>きゅうなあめ</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -761,15 +753,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>このたび</t>
+          <t>直る</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>此次，这次</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>修好；改正</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>なおる</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -778,16 +774,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>みたいだ</t>
+          <t>〜に応じて</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>好像...，像...一样</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+          <t>根据...，按照...</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>〜におうじて</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>“～にこたえて”响应</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -795,40 +799,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>このたび</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>根源,原因</t>
+          <t>此次，这次</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>“もっと”更加…;更进一步</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>急な雨</t>
+          <t>ようがない</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>急雨，阵雨</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>きゅうなあめ</t>
-        </is>
-      </c>
+          <t>没法...，无法...</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -837,16 +833,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>おそらく〜でしょう・だろう</t>
+          <t>〜に決まる</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>大概...吧，恐怕...吧</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>一定是...，肯定是...</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>〜にきまる</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>同“～に違いない”</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -854,19 +858,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>話</t>
+          <t>おすすめです</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>这件事</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>はなし</t>
-        </is>
-      </c>
+          <t>推荐</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -875,39 +875,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>って</t>
+          <t>看病</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>（口语）表示引用或主题</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>护理，照顾</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>かんびょう</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>持ち歩く</t>
+          <t>落ち込んだ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>随身携带</t>
+          <t>心情低落，消沉</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>もちあるく</t>
+          <t>おちこんだ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>“持参”携带</t>
+          <t>“落ち着かせる”使…平静</t>
         </is>
       </c>
     </row>
@@ -917,19 +921,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>直る</t>
+          <t>〜である</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>修好；改正</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>なおる</t>
-        </is>
-      </c>
+          <t>是...（です的书面语）</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">

--- a/GRAMMAR/6_19_12.xlsx
+++ b/GRAMMAR/6_19_12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -463,10 +463,15 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -480,6 +485,11 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,6 +507,11 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -514,6 +529,11 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -531,6 +551,11 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -556,6 +581,11 @@
           <t>同“～に違いない”</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -577,6 +607,11 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -598,10 +633,15 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -615,6 +655,11 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -632,10 +677,15 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -655,6 +705,11 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>“落ち着かせる”使…平静</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -678,6 +733,11 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -703,6 +763,11 @@
           <t>“～にこたえて”响应</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -720,6 +785,11 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -737,10 +807,15 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -754,6 +829,11 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -771,6 +851,11 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -788,6 +873,11 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -809,6 +899,11 @@
           <t>“もっと”更加…;更进一步</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -830,6 +925,11 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -847,6 +947,11 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -868,6 +973,11 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -885,6 +995,11 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -910,10 +1025,15 @@
           <t>“持参”携带</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -931,10 +1051,15 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -950,6 +1075,11 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>“わけではない”并不是</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
